--- a/test-data/files/Answer_Key_Expected_Results.xlsx
+++ b/test-data/files/Answer_Key_Expected_Results.xlsx
@@ -450,7 +450,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <cols>
     <col min="1" max="1" width="52.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -533,25 +533,33 @@
         <v>Skipped junk rows in books (warning banner)</v>
       </c>
       <c r="B10" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="str">
+        <v>Footer rows auto-removed ("Grand Total" line)</v>
+      </c>
+      <c r="B11" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="str">
         <v>ITC at risk (₹)</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B12" s="2">
         <v>9270.1</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="str">
+    <row r="14">
+      <c r="A14" s="2" t="str">
         <v>* T19 is a known limitation: matching uses taxable value, so a tax-only difference stays green.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B14"/>
   </ignoredErrors>
 </worksheet>
 </file>
